--- a/DateBase/orders/Nha Thu_2026-9-19.xlsx
+++ b/DateBase/orders/Nha Thu_2026-9-19.xlsx
@@ -849,6 +849,9 @@
       <c r="G2" t="str">
         <v>010106101515101051010155510102105102081051051069138101015101051010105</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
